--- a/BWI/bestwine_output/bestwine_Venezuela.xlsx
+++ b/BWI/bestwine_output/bestwine_Venezuela.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA31"/>
+  <dimension ref="A1:AA33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3648,6 +3648,232 @@
       <c r="Z31" s="2" t="inlineStr"/>
       <c r="AA31" s="2" t="inlineStr"/>
     </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Tamayo &amp; Cia, S.a.</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Tamayo &amp; Cia, S.a.</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>21679</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Caracas</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Distrito Capital, Libertador</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Avenida Nueva Granada</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>1041</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>http://tamayo.com.ve</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>tamayociaoficial@gmail.com</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>+58 212-6034786</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>1903</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>J000358427</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/tamayo-&amp;-c-a-sa</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/tamayociaoficial</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/tamayociaofic</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr"/>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>Antonio Torres</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr"/>
+      <c r="Z32" s="2" t="inlineStr"/>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/antonio-torres-4920257b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Tamayo &amp; Cia, S.a.</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Tamayo &amp; Cia, S.a.</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>21679</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Caracas</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Distrito Capital, Libertador</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Avenida Nueva Granada</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>1041</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>http://tamayo.com.ve</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>tamayociaoficial@gmail.com</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>+58 212-6034786</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>1903</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>J000358427</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/tamayo-&amp;-c-a-sa</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/tamayociaoficial</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/tamayociaofic</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr"/>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>Maria Garcia</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing Manager</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr"/>
+      <c r="Z33" s="2" t="inlineStr"/>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/maria-garcia-10248b127/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Venezuela.xlsx
+++ b/BWI/bestwine_output/bestwine_Venezuela.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA33"/>
+  <dimension ref="A1:AA35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3874,6 +3874,232 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Tamayo &amp; Cia, S.a.</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Tamayo &amp; Cia, S.a.</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>21679</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Caracas</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Distrito Capital, Libertador</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Avenida Nueva Granada</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>1041</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>http://tamayo.com.ve</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>tamayociaoficial@gmail.com</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>+58 212-6034786</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>1903</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>J000358427</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/tamayo-&amp;-c-a-sa</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/tamayociaoficial</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/tamayociaofic</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr"/>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>Antonio Torres</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr"/>
+      <c r="Z34" s="2" t="inlineStr"/>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/antonio-torres-4920257b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Tamayo &amp; Cia, S.a.</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Tamayo &amp; Cia, S.a.</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>21679</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Caracas</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Distrito Capital, Libertador</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Avenida Nueva Granada</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>1041</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>http://tamayo.com.ve</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>tamayociaoficial@gmail.com</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>+58 212-6034786</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>1903</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>J000358427</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/tamayo-&amp;-c-a-sa</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/tamayociaoficial</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/tamayociaofic</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr"/>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>Maria Garcia</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing Manager</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr"/>
+      <c r="Z35" s="2" t="inlineStr"/>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/maria-garcia-10248b127/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Venezuela.xlsx
+++ b/BWI/bestwine_output/bestwine_Venezuela.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA35"/>
+  <dimension ref="A1:AA37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -4100,6 +4100,204 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Bodca Bodegon C.a.</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Bodca Bodegon C.a.</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>56325</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Caracas</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>D.F.</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Av. Los Próceres, C.c. Alto Prado. Local 3 Pb Parte Posterior Del Centro Comercial</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>1080</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>https://bodcabodegon.com</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>ventas@bodcabodegon.com</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>+58 274-2443792</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr"/>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/BodcaBodegonca/</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bodcabodegon</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>https://twitter.com/bodcabodegon</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr"/>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>Keyffer Salas</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr"/>
+      <c r="Z36" s="2" t="inlineStr"/>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/keyffer-salas-b9a1b390/</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Productora Enotria C.a.</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Productora Enotria C.a.</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>122565</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Guarenas</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Miranda, Municipio Ambrosio Plaza</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Urbanización Santa Cruz, Calle el Oficio Manzana 4, Parcela 4</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>1220</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>https://productora-enotria.com</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>infor.enotria@gmail.com</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>+58 212-7167454</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>1983</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>J-00170836-7</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/_enotria</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr"/>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>Giovanni Cappellin</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr"/>
+      <c r="Z37" s="2" t="inlineStr"/>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/giovanni-cappellin-a46a24172</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
